--- a/backend/data/financials_by_company/1F3.SI.xlsx
+++ b/backend/data/financials_by_company/1F3.SI.xlsx
@@ -3924,10 +3924,8 @@
           <t>George Town</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10450</t>
-        </is>
+      <c r="D2" t="n">
+        <v>10450</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4144,7 +4142,7 @@
         <v>-14951000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
         <v>0.6830000000000001</v>
@@ -4396,7 +4394,7 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
